--- a/documentation/BUG REPORT.xlsx
+++ b/documentation/BUG REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Worpdress Blog Manual Testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CDC12F-BB8D-4A2A-900C-CA4DB03964EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD3DFA0-5728-4B77-8F28-F5ACC32D3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{99208258-F126-4562-88E1-3DA1320E1714}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Module</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Registration Module</t>
+  </si>
+  <si>
+    <t>Login Module</t>
   </si>
   <si>
     <t>BUG ID</t>
@@ -86,6 +89,25 @@
   </si>
   <si>
     <t>Syaif</t>
+  </si>
+  <si>
+    <t>Verify error when email not registered</t>
+  </si>
+  <si>
+    <t>BUG-02</t>
+  </si>
+  <si>
+    <t>System appears invalid email but the message not "Email and passwordincorrect" 
+(Must changed)</t>
+  </si>
+  <si>
+    <t>1. Enter unregistered email 
+2. Enter any password 
+3. Click Login</t>
+  </si>
+  <si>
+    <t>Chrome v145 /
+Windows 12</t>
   </si>
 </sst>
 </file>
@@ -516,39 +538,39 @@
   <sheetData>
     <row r="3" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="3:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -557,38 +579,58 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="L5" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C6" s="5"/>

--- a/documentation/BUG REPORT.xlsx
+++ b/documentation/BUG REPORT.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Worpdress Blog Manual Testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD3DFA0-5728-4B77-8F28-F5ACC32D3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB7AE10-9984-4C59-BDDC-E48770721E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{99208258-F126-4562-88E1-3DA1320E1714}"/>
   </bookViews>
   <sheets>
-    <sheet name="Registration Module" sheetId="1" r:id="rId1"/>
+    <sheet name="BUG REPORT" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -202,9 +202,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -521,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A25FA9-3B9D-44C9-86EA-75B357B6CC75}">
-  <dimension ref="C3:L9"/>
+  <dimension ref="C3:L5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -632,54 +629,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
